--- a/clustering/8 subclusters (factoriescap_s (usage) 0 visnorm).xlsx
+++ b/clustering/8 subclusters (factoriescap_s (usage) 0 visnorm).xlsx
@@ -636,12 +636,8 @@
       <c r="A13" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="2">
-        <v>0</v>
-      </c>
-      <c r="C13" s="2">
-        <v>0</v>
-      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
       <c r="D13" s="5">
         <f>D2/$C2</f>
         <v>3.0755299292195303E-2</v>
@@ -676,12 +672,8 @@
       <c r="A15" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="2">
-        <v>0</v>
-      </c>
-      <c r="C15" s="2">
-        <v>0</v>
-      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
       <c r="D15" s="5">
         <f t="shared" ref="D15:E15" si="1">D4/$C4</f>
         <v>3.9905430577446624E-2</v>
@@ -716,12 +708,8 @@
       <c r="A17" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="2">
-        <v>0</v>
-      </c>
-      <c r="C17" s="2">
-        <v>0</v>
-      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
       <c r="D17" s="5">
         <f t="shared" ref="D17:E17" si="3">D6/$C6</f>
         <v>4.6503178928247069E-2</v>
@@ -756,12 +744,8 @@
       <c r="A19" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="2">
-        <v>0</v>
-      </c>
-      <c r="C19" s="2">
-        <v>0</v>
-      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
       <c r="D19" s="5">
         <f t="shared" ref="D19:E19" si="5">D8/$C8</f>
         <v>4.0811882728050378E-2</v>

--- a/clustering/8 subclusters (factoriescap_s (usage) 0 visnorm).xlsx
+++ b/clustering/8 subclusters (factoriescap_s (usage) 0 visnorm).xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="16">
   <si>
     <t>clust</t>
   </si>
@@ -58,6 +58,15 @@
   </si>
   <si>
     <t>3 (upper)</t>
+  </si>
+  <si>
+    <t>AIusage_s % in IT</t>
+  </si>
+  <si>
+    <t>BDusage_s % in IT</t>
+  </si>
+  <si>
+    <t>Медианы кластеров</t>
   </si>
 </sst>
 </file>
@@ -68,7 +77,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _₽_-;\-* #,##0.00\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="#,##0.00_ ;\-#,##0.00\ "/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -89,6 +98,20 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -128,7 +151,7 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -148,6 +171,15 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -165,6 +197,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>447675</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>85726</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>157164</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Рисунок 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6210300" y="85726"/>
+          <a:ext cx="4667250" cy="3500438"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -452,7 +533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -460,6 +541,8 @@
     <col min="3" max="3" width="16.7109375" customWidth="1"/>
     <col min="4" max="4" width="14.28515625" customWidth="1"/>
     <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="6" max="6" width="22.5703125" customWidth="1"/>
+    <col min="7" max="7" width="17.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -704,7 +787,7 @@
         <v>0.22713662417657612</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>9</v>
       </c>
@@ -719,7 +802,7 @@
         <v>0.15267938237965478</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>10</v>
       </c>
@@ -740,7 +823,7 @@
         <v>0.26418840282056538</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>11</v>
       </c>
@@ -755,7 +838,7 @@
         <v>0.18004899292324417</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>12</v>
       </c>
@@ -776,8 +859,208 @@
         <v>0.23318551510456995</v>
       </c>
     </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>0</v>
+      </c>
+      <c r="B25" s="8">
+        <v>239465.7845999992</v>
+      </c>
+      <c r="C25" s="2">
+        <v>125.99999999999901</v>
+      </c>
+      <c r="D25" s="2">
+        <v>3.9999999999999818</v>
+      </c>
+      <c r="E25" s="2">
+        <v>22.999999999999751</v>
+      </c>
+      <c r="F25" s="5">
+        <f>D25/C25</f>
+        <v>3.1746031746031855E-2</v>
+      </c>
+      <c r="G25" s="5">
+        <f>E25/C25</f>
+        <v>0.182539682539682</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>1</v>
+      </c>
+      <c r="B26" s="8">
+        <v>1433541.3485999971</v>
+      </c>
+      <c r="C26" s="2">
+        <v>1163.4999999999991</v>
+      </c>
+      <c r="D26" s="2">
+        <v>49.499999999999943</v>
+      </c>
+      <c r="E26" s="2">
+        <v>241.99999999999969</v>
+      </c>
+      <c r="F26" s="5">
+        <f t="shared" ref="F26:F28" si="7">D26/C26</f>
+        <v>4.2544048130640291E-2</v>
+      </c>
+      <c r="G26" s="5">
+        <f t="shared" ref="G26:G28" si="8">E26/C26</f>
+        <v>0.2079931241942414</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>2</v>
+      </c>
+      <c r="B27" s="8">
+        <v>2814023.5847999961</v>
+      </c>
+      <c r="C27" s="2">
+        <v>2743.5</v>
+      </c>
+      <c r="D27" s="2">
+        <v>127.5</v>
+      </c>
+      <c r="E27" s="2">
+        <v>533.49999999999955</v>
+      </c>
+      <c r="F27" s="5">
+        <f t="shared" si="7"/>
+        <v>4.6473482777474026E-2</v>
+      </c>
+      <c r="G27" s="5">
+        <f t="shared" si="8"/>
+        <v>0.19445963185711665</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>3</v>
+      </c>
+      <c r="B28" s="8">
+        <v>860049.56519999588</v>
+      </c>
+      <c r="C28" s="2">
+        <v>460.99999999999949</v>
+      </c>
+      <c r="D28" s="2">
+        <v>18.999999999999972</v>
+      </c>
+      <c r="E28" s="2">
+        <v>98.999999999999901</v>
+      </c>
+      <c r="F28" s="5">
+        <f t="shared" si="7"/>
+        <v>4.1214750542299332E-2</v>
+      </c>
+      <c r="G28" s="5">
+        <f t="shared" si="8"/>
+        <v>0.21475054229934926</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B9">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C9">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D9">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E9">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B25:B28">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C25:C28">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D25:D28">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -789,7 +1072,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C9">
+  <conditionalFormatting sqref="E25:E28">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -801,7 +1084,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D9">
+  <conditionalFormatting sqref="F25:F28">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -813,7 +1096,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E9">
+  <conditionalFormatting sqref="G25:G28">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -827,5 +1110,6 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/clustering/8 subclusters (factoriescap_s (usage) 0 visnorm).xlsx
+++ b/clustering/8 subclusters (factoriescap_s (usage) 0 visnorm).xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="14">
   <si>
     <t>clust</t>
   </si>
@@ -58,12 +58,6 @@
   </si>
   <si>
     <t>3 (upper)</t>
-  </si>
-  <si>
-    <t>AIusage_s % in IT</t>
-  </si>
-  <si>
-    <t>BDusage_s % in IT</t>
   </si>
   <si>
     <t>Медианы кластеров</t>
@@ -151,7 +145,7 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -178,6 +172,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -738,7 +738,7 @@
         <f>B3/B2</f>
         <v>11.470048255219691</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="10">
         <f>C3/C2</f>
         <v>3.6711472454423846</v>
       </c>
@@ -774,7 +774,7 @@
         <f>B5/B4</f>
         <v>2.8295585064297497</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="11">
         <f>C5/C4</f>
         <v>1.6748817882218094</v>
       </c>
@@ -792,7 +792,7 @@
         <v>9</v>
       </c>
       <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
+      <c r="C17" s="3"/>
       <c r="D17" s="5">
         <f t="shared" ref="D17:E17" si="3">D6/$C6</f>
         <v>4.6503178928247069E-2</v>
@@ -810,7 +810,7 @@
         <f>B7/B6</f>
         <v>3.1940654651453433</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="11">
         <f>C7/C6</f>
         <v>1.3267029972752049</v>
       </c>
@@ -828,7 +828,7 @@
         <v>11</v>
       </c>
       <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
+      <c r="C19" s="3"/>
       <c r="D19" s="5">
         <f t="shared" ref="D19:E19" si="5">D8/$C8</f>
         <v>4.0811882728050378E-2</v>
@@ -846,7 +846,7 @@
         <f>B9/B8</f>
         <v>5.5472790436468067</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C20" s="11">
         <f>C9/C8</f>
         <v>1.7569406641262946</v>
       </c>
@@ -861,7 +861,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -880,12 +880,8 @@
       <c r="E24" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F24" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
@@ -903,14 +899,8 @@
       <c r="E25" s="2">
         <v>22.999999999999751</v>
       </c>
-      <c r="F25" s="5">
-        <f>D25/C25</f>
-        <v>3.1746031746031855E-2</v>
-      </c>
-      <c r="G25" s="5">
-        <f>E25/C25</f>
-        <v>0.182539682539682</v>
-      </c>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
@@ -928,14 +918,8 @@
       <c r="E26" s="2">
         <v>241.99999999999969</v>
       </c>
-      <c r="F26" s="5">
-        <f t="shared" ref="F26:F28" si="7">D26/C26</f>
-        <v>4.2544048130640291E-2</v>
-      </c>
-      <c r="G26" s="5">
-        <f t="shared" ref="G26:G28" si="8">E26/C26</f>
-        <v>0.2079931241942414</v>
-      </c>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
@@ -953,14 +937,8 @@
       <c r="E27" s="2">
         <v>533.49999999999955</v>
       </c>
-      <c r="F27" s="5">
-        <f t="shared" si="7"/>
-        <v>4.6473482777474026E-2</v>
-      </c>
-      <c r="G27" s="5">
-        <f t="shared" si="8"/>
-        <v>0.19445963185711665</v>
-      </c>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
@@ -978,14 +956,8 @@
       <c r="E28" s="2">
         <v>98.999999999999901</v>
       </c>
-      <c r="F28" s="5">
-        <f t="shared" si="7"/>
-        <v>4.1214750542299332E-2</v>
-      </c>
-      <c r="G28" s="5">
-        <f t="shared" si="8"/>
-        <v>0.21475054229934926</v>
-      </c>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B9">

--- a/clustering/8 subclusters (factoriescap_s (usage) 0 visnorm).xlsx
+++ b/clustering/8 subclusters (factoriescap_s (usage) 0 visnorm).xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="14">
   <si>
     <t>clust</t>
   </si>
@@ -67,9 +67,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _₽_-;\-* #,##0.00\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="#,##0.00_ ;\-#,##0.00\ "/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -83,8 +84,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>
@@ -106,17 +105,25 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -139,13 +146,88 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -156,28 +238,64 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -203,16 +321,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>447675</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>19051</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>85726</xdr:rowOff>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>157164</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>204789</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -235,8 +353,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6210300" y="85726"/>
-          <a:ext cx="4667250" cy="3500438"/>
+          <a:off x="5495926" y="85725"/>
+          <a:ext cx="5672138" cy="3781425"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -533,16 +651,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.5703125" customWidth="1"/>
-    <col min="7" max="7" width="17.42578125" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -563,405 +678,395 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2">
+        <v>504459.74453636142</v>
+      </c>
+      <c r="C2" s="3">
+        <v>411.29545454545382</v>
+      </c>
+      <c r="D2" s="3">
+        <v>18.909090909090871</v>
+      </c>
+      <c r="E2" s="3">
+        <v>92.88636363636337</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2">
+        <v>2972238.8305590879</v>
+      </c>
+      <c r="C3" s="3">
+        <v>539.49999999999932</v>
+      </c>
+      <c r="D3" s="3">
+        <v>22.340909090909062</v>
+      </c>
+      <c r="E3" s="3">
+        <v>111.54545454545431</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2">
+        <v>895395.92730666487</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1336.5333333333331</v>
+      </c>
+      <c r="D4" s="3">
+        <v>50.599999999999987</v>
+      </c>
+      <c r="E4" s="3">
+        <v>275.26666666666642</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2">
+        <v>2551882.202013331</v>
+      </c>
+      <c r="C5" s="3">
+        <v>1155.399999999999</v>
+      </c>
+      <c r="D5" s="3">
+        <v>45.933333333333287</v>
+      </c>
+      <c r="E5" s="3">
+        <v>231.66666666666629</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2">
+        <v>1561252.205759997</v>
+      </c>
+      <c r="C6" s="3">
+        <v>2616.599999999999</v>
+      </c>
+      <c r="D6" s="3">
+        <v>114.2</v>
+      </c>
+      <c r="E6" s="3">
+        <v>514.99999999999977</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>2</v>
+      </c>
+      <c r="B7" s="2">
+        <v>4986741.752799998</v>
+      </c>
+      <c r="C7" s="3">
+        <v>2506.8000000000002</v>
+      </c>
+      <c r="D7" s="3">
+        <v>129.6</v>
+      </c>
+      <c r="E7" s="3">
+        <v>592.99999999999966</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>3</v>
+      </c>
+      <c r="B8" s="2">
+        <v>101373.9196576899</v>
+      </c>
+      <c r="C8" s="3">
+        <v>91.490384615383775</v>
+      </c>
+      <c r="D8" s="3">
+        <v>3.4230769230768798</v>
+      </c>
+      <c r="E8" s="3">
+        <v>17.221153846153609</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>3</v>
+      </c>
+      <c r="B9" s="2">
+        <v>1135779.941959613</v>
+      </c>
+      <c r="C9" s="3">
+        <v>181.5865384615376</v>
+      </c>
+      <c r="D9" s="3">
+        <v>7.3942307692307319</v>
+      </c>
+      <c r="E9" s="3">
+        <v>36.28846153846127</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3">
-        <v>105012.1823962593</v>
-      </c>
-      <c r="C2" s="3">
-        <v>60.056603773584072</v>
-      </c>
-      <c r="D2" s="3">
-        <v>1.8470588235293639</v>
-      </c>
-      <c r="E2" s="3">
-        <v>10.77570093457922</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="20">
+        <f>D2/$C2</f>
+        <v>4.597447090678012E-2</v>
+      </c>
+      <c r="E13" s="21">
+        <f>E2/$C2</f>
+        <v>0.22583853677405069</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3">
-        <v>1204494.7994710261</v>
-      </c>
-      <c r="C3" s="3">
-        <v>220.47663551401789</v>
-      </c>
-      <c r="D3" s="3">
-        <v>9.0285714285713858</v>
-      </c>
-      <c r="E3" s="3">
-        <v>46.104761904761602</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="B14" s="10">
+        <f>B3/B2</f>
+        <v>5.8919247031114672</v>
+      </c>
+      <c r="C14" s="11">
+        <f>C3/C2</f>
+        <v>1.3117091230590712</v>
+      </c>
+      <c r="D14" s="12">
+        <f t="shared" ref="D14:E20" si="0">D3/$C3</f>
+        <v>4.1410396832083578E-2</v>
+      </c>
+      <c r="E14" s="13">
+        <f t="shared" si="0"/>
+        <v>0.2067570983233632</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="3">
-        <v>901865.85511999822</v>
-      </c>
-      <c r="C4" s="3">
-        <v>930.53333333333251</v>
-      </c>
-      <c r="D4" s="3">
-        <v>37.133333333333297</v>
-      </c>
-      <c r="E4" s="3">
-        <v>160.2666666666664</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="8">
+        <f t="shared" si="0"/>
+        <v>3.7859138068635272E-2</v>
+      </c>
+      <c r="E15" s="21">
+        <f t="shared" si="0"/>
+        <v>0.20595570630486817</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="3">
-        <v>2551882.202013331</v>
-      </c>
-      <c r="C5" s="3">
-        <v>1558.5333333333331</v>
-      </c>
-      <c r="D5" s="3">
-        <v>60.999999999999972</v>
-      </c>
-      <c r="E5" s="3">
-        <v>353.99999999999972</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="B16" s="10">
+        <f>B5/B4</f>
+        <v>2.8500042541955128</v>
+      </c>
+      <c r="C16" s="15">
+        <f>C5/C4</f>
+        <v>0.86447525937749337</v>
+      </c>
+      <c r="D16" s="16">
+        <f t="shared" si="0"/>
+        <v>3.9755351681957179E-2</v>
+      </c>
+      <c r="E16" s="17">
+        <f t="shared" si="0"/>
+        <v>0.20050776066008871</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="3">
-        <v>1561252.205759997</v>
-      </c>
-      <c r="C6" s="3">
-        <v>2201.9999999999991</v>
-      </c>
-      <c r="D6" s="3">
-        <v>102.4</v>
-      </c>
-      <c r="E6" s="3">
-        <v>336.1999999999997</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="B17" s="7"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="8">
+        <f t="shared" si="0"/>
+        <v>4.364442406175955E-2</v>
+      </c>
+      <c r="E17" s="14">
+        <f t="shared" si="0"/>
+        <v>0.19682030115416951</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="3">
-        <v>4986741.752799998</v>
-      </c>
-      <c r="C7" s="3">
-        <v>2921.4</v>
-      </c>
-      <c r="D7" s="3">
-        <v>141.39999999999989</v>
-      </c>
-      <c r="E7" s="3">
-        <v>771.79999999999973</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="3">
-        <v>528784.78545365622</v>
-      </c>
-      <c r="C8" s="3">
-        <v>358.43902439024311</v>
-      </c>
-      <c r="D8" s="3">
-        <v>14.628571428571391</v>
-      </c>
-      <c r="E8" s="3">
-        <v>64.536585365853426</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="3">
-        <v>2933316.7589463401</v>
-      </c>
-      <c r="C9" s="3">
-        <v>629.75609756097481</v>
-      </c>
-      <c r="D9" s="3">
-        <v>27.439024390243869</v>
-      </c>
-      <c r="E9" s="3">
-        <v>146.84999999999971</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="5">
-        <f>D2/$C2</f>
-        <v>3.0755299292195303E-2</v>
-      </c>
-      <c r="E13" s="6">
-        <f>E2/$C2</f>
-        <v>0.17942574600462036</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="4">
-        <f>B3/B2</f>
-        <v>11.470048255219691</v>
-      </c>
-      <c r="C14" s="10">
-        <f>C3/C2</f>
-        <v>3.6711472454423846</v>
-      </c>
-      <c r="D14" s="5">
-        <f t="shared" ref="D14:E14" si="0">D3/$C3</f>
-        <v>4.095024131478707E-2</v>
-      </c>
-      <c r="E14" s="6">
-        <f t="shared" si="0"/>
-        <v>0.20911404873932896</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="5">
-        <f t="shared" ref="D15:E15" si="1">D4/$C4</f>
-        <v>3.9905430577446624E-2</v>
-      </c>
-      <c r="E15" s="5">
-        <f t="shared" si="1"/>
-        <v>0.17223097865023629</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="4">
-        <f>B5/B4</f>
-        <v>2.8295585064297497</v>
-      </c>
-      <c r="C16" s="11">
-        <f>C5/C4</f>
-        <v>1.6748817882218094</v>
-      </c>
-      <c r="D16" s="5">
-        <f t="shared" ref="D16:E16" si="2">D5/$C5</f>
-        <v>3.9139361793138837E-2</v>
-      </c>
-      <c r="E16" s="5">
-        <f t="shared" si="2"/>
-        <v>0.22713662417657612</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="5">
-        <f t="shared" ref="D17:E17" si="3">D6/$C6</f>
-        <v>4.6503178928247069E-2</v>
-      </c>
-      <c r="E17" s="5">
-        <f t="shared" si="3"/>
-        <v>0.15267938237965478</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B18" s="4">
+      <c r="B18" s="10">
         <f>B7/B6</f>
         <v>3.1940654651453433</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="15">
         <f>C7/C6</f>
-        <v>1.3267029972752049</v>
-      </c>
-      <c r="D18" s="5">
-        <f t="shared" ref="D18:E18" si="4">D7/$C7</f>
-        <v>4.8401451358937454E-2</v>
-      </c>
-      <c r="E18" s="5">
-        <f t="shared" si="4"/>
-        <v>0.26418840282056538</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+        <v>0.95803714744324742</v>
+      </c>
+      <c r="D18" s="16">
+        <f t="shared" si="0"/>
+        <v>5.1699377692675914E-2</v>
+      </c>
+      <c r="E18" s="22">
+        <f t="shared" si="0"/>
+        <v>0.23655656614009879</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="5">
-        <f t="shared" ref="D19:E19" si="5">D8/$C8</f>
-        <v>4.0811882728050378E-2</v>
-      </c>
-      <c r="E19" s="5">
-        <f t="shared" si="5"/>
-        <v>0.18004899292324417</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+      <c r="B19" s="7"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="8">
+        <f t="shared" si="0"/>
+        <v>3.741460851287428E-2</v>
+      </c>
+      <c r="E19" s="14">
+        <f t="shared" si="0"/>
+        <v>0.18822911192853303</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="10">
         <f>B9/B8</f>
-        <v>5.5472790436468067</v>
-      </c>
-      <c r="C20" s="11">
+        <v>11.20386728455218</v>
+      </c>
+      <c r="C20" s="19">
         <f>C9/C8</f>
-        <v>1.7569406641262946</v>
-      </c>
-      <c r="D20" s="5">
-        <f t="shared" ref="D20:E20" si="6">D9/$C9</f>
-        <v>4.3570875290472502E-2</v>
-      </c>
-      <c r="E20" s="5">
-        <f t="shared" si="6"/>
-        <v>0.23318551510456995</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
+        <v>1.9847609038360572</v>
+      </c>
+      <c r="D20" s="16">
+        <f t="shared" si="0"/>
+        <v>4.072014826581942E-2</v>
+      </c>
+      <c r="E20" s="22">
+        <f t="shared" si="0"/>
+        <v>0.19984114376489223</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B22" s="23" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B23" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C23" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D23" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E23" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>0</v>
+      </c>
+      <c r="B24" s="2">
+        <v>820608.91839999636</v>
+      </c>
+      <c r="C24" s="2">
+        <v>431.9999999999996</v>
+      </c>
+      <c r="D24" s="2">
+        <v>18.999999999999972</v>
+      </c>
+      <c r="E24" s="2">
+        <v>96.000000000000014</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <v>0</v>
-      </c>
-      <c r="B25" s="8">
-        <v>239465.7845999992</v>
+        <v>1</v>
+      </c>
+      <c r="B25" s="2">
+        <v>1391118.346799999</v>
       </c>
       <c r="C25" s="2">
-        <v>125.99999999999901</v>
+        <v>1141.9999999999991</v>
       </c>
       <c r="D25" s="2">
+        <v>48.999999999999943</v>
+      </c>
+      <c r="E25" s="2">
+        <v>236.99999999999949</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>2</v>
+      </c>
+      <c r="B26" s="2">
+        <v>2814023.5847999961</v>
+      </c>
+      <c r="C26" s="2">
+        <v>2743.5</v>
+      </c>
+      <c r="D26" s="2">
+        <v>127.5</v>
+      </c>
+      <c r="E26" s="2">
+        <v>533.49999999999955</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>3</v>
+      </c>
+      <c r="B27" s="2">
+        <v>230117.38799999989</v>
+      </c>
+      <c r="C27" s="2">
+        <v>123.99999999999849</v>
+      </c>
+      <c r="D27" s="2">
         <v>3.9999999999999818</v>
       </c>
-      <c r="E25" s="2">
-        <v>22.999999999999751</v>
-      </c>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
-        <v>1</v>
-      </c>
-      <c r="B26" s="8">
-        <v>1433541.3485999971</v>
-      </c>
-      <c r="C26" s="2">
-        <v>1163.4999999999991</v>
-      </c>
-      <c r="D26" s="2">
-        <v>49.499999999999943</v>
-      </c>
-      <c r="E26" s="2">
-        <v>241.99999999999969</v>
-      </c>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
-        <v>2</v>
-      </c>
-      <c r="B27" s="8">
-        <v>2814023.5847999961</v>
-      </c>
-      <c r="C27" s="2">
-        <v>2743.5</v>
-      </c>
-      <c r="D27" s="2">
-        <v>127.5</v>
-      </c>
       <c r="E27" s="2">
-        <v>533.49999999999955</v>
-      </c>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
-        <v>3</v>
-      </c>
-      <c r="B28" s="8">
-        <v>860049.56519999588</v>
-      </c>
-      <c r="C28" s="2">
-        <v>460.99999999999949</v>
-      </c>
-      <c r="D28" s="2">
-        <v>18.999999999999972</v>
-      </c>
-      <c r="E28" s="2">
-        <v>98.999999999999901</v>
-      </c>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
+        <v>21.99999999999979</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B9">
-    <cfRule type="colorScale" priority="10">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -973,7 +1078,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C9">
-    <cfRule type="colorScale" priority="9">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -985,7 +1090,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D9">
-    <cfRule type="colorScale" priority="8">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -997,78 +1102,6 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E9">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B25:B28">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C25:C28">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D25:D28">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E25:E28">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F25:F28">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G25:G28">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>

--- a/clustering/8 subclusters (factoriescap_s (usage) 0 visnorm).xlsx
+++ b/clustering/8 subclusters (factoriescap_s (usage) 0 visnorm).xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="14">
   <si>
     <t>clust</t>
   </si>
@@ -84,6 +84,8 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>
@@ -227,7 +229,7 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -296,6 +298,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -651,7 +656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.28515625" customWidth="1"/>
@@ -1064,8 +1069,197 @@
         <v>21.99999999999979</v>
       </c>
     </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>0</v>
+      </c>
+      <c r="B31" s="2">
+        <v>239537.8512039996</v>
+      </c>
+      <c r="C31" s="2">
+        <v>1418</v>
+      </c>
+      <c r="D31" s="24">
+        <f>D24/$C24</f>
+        <v>4.3981481481481455E-2</v>
+      </c>
+      <c r="E31" s="24">
+        <f>E24/$C24</f>
+        <v>0.22222222222222246</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>1</v>
+      </c>
+      <c r="B32" s="2">
+        <v>1615284.14922</v>
+      </c>
+      <c r="C32" s="2">
+        <v>5560.5</v>
+      </c>
+      <c r="D32" s="24">
+        <f t="shared" ref="D32:E34" si="1">D25/$C25</f>
+        <v>4.290718038528895E-2</v>
+      </c>
+      <c r="E32" s="24">
+        <f t="shared" si="1"/>
+        <v>0.20753064798598922</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>2</v>
+      </c>
+      <c r="B33" s="2">
+        <v>1418484.1690199999</v>
+      </c>
+      <c r="C33" s="2">
+        <v>4248.5</v>
+      </c>
+      <c r="D33" s="24">
+        <f t="shared" si="1"/>
+        <v>4.6473482777474026E-2</v>
+      </c>
+      <c r="E33" s="24">
+        <f t="shared" si="1"/>
+        <v>0.19445963185711665</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>3</v>
+      </c>
+      <c r="B34" s="2">
+        <v>578868.78119999985</v>
+      </c>
+      <c r="C34" s="2">
+        <v>2406.9999999999991</v>
+      </c>
+      <c r="D34" s="24">
+        <f t="shared" si="1"/>
+        <v>3.2258064516129274E-2</v>
+      </c>
+      <c r="E34" s="24">
+        <f t="shared" si="1"/>
+        <v>0.17741935483871013</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B9">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C9">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D9">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E9">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B24:B27">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C24:C27">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D24:D27">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E24:E27">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31:B34">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -1077,7 +1271,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C9">
+  <conditionalFormatting sqref="C31:C34">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -1089,7 +1283,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D9">
+  <conditionalFormatting sqref="D31:D34">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -1101,7 +1295,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E9">
+  <conditionalFormatting sqref="E31:E34">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
